--- a/docentes/Rivera Serra Alma Lilian - Estadisticos 20241.xlsx
+++ b/docentes/Rivera Serra Alma Lilian - Estadisticos 20241.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="23">
   <si>
     <t>Mat</t>
   </si>
@@ -77,6 +77,15 @@
   </si>
   <si>
     <t>Reprobadas</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>TZITZIHUA</t>
+  </si>
+  <si>
+    <t>MIRIAM</t>
   </si>
 </sst>
 </file>
@@ -594,16 +603,19 @@
         <v>25</v>
       </c>
       <c r="D2">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>92</v>
+      </c>
+      <c r="H2">
+        <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -617,16 +629,19 @@
         <v>19</v>
       </c>
       <c r="D3">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>89.47</v>
+      </c>
+      <c r="H3">
+        <v>7.1</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -640,16 +655,19 @@
         <v>28</v>
       </c>
       <c r="D4">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>92.86</v>
+      </c>
+      <c r="H4">
+        <v>7.9</v>
       </c>
     </row>
   </sheetData>
@@ -714,7 +732,7 @@
         <v>92</v>
       </c>
       <c r="H2">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -731,16 +749,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F3">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G3">
-        <v>73.68000000000001</v>
+        <v>89.47</v>
       </c>
       <c r="H3">
-        <v>7.1</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -757,16 +775,16 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F4">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="G4">
-        <v>82.14</v>
+        <v>92.86</v>
       </c>
       <c r="H4">
-        <v>7.9</v>
+        <v>8.4</v>
       </c>
     </row>
   </sheetData>
@@ -776,7 +794,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -806,6 +824,29 @@
         <v>19</v>
       </c>
     </row>
+    <row r="2" spans="1:7">
+      <c r="A2">
+        <v>23330051920233</v>
+      </c>
+      <c r="B2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G2">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/docentes/Rivera Serra Alma Lilian - Estadisticos 20241.xlsx
+++ b/docentes/Rivera Serra Alma Lilian - Estadisticos 20241.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="29">
   <si>
     <t>Mat</t>
   </si>
@@ -79,10 +79,28 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>ESTRADA</t>
+  </si>
+  <si>
     <t>GONZALEZ</t>
   </si>
   <si>
+    <t>SARMIENTO</t>
+  </si>
+  <si>
+    <t>SAN JUAN</t>
+  </si>
+  <si>
     <t>TZITZIHUA</t>
+  </si>
+  <si>
+    <t>EDUARDO</t>
+  </si>
+  <si>
+    <t>JOSE MARCOS</t>
   </si>
   <si>
     <t>MIRIAM</t>
@@ -794,7 +812,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -826,16 +844,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>23330051920233</v>
+        <v>23330051920236</v>
       </c>
       <c r="B2" t="s">
         <v>20</v>
       </c>
       <c r="C2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D2" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -845,6 +863,52 @@
       </c>
       <c r="G2">
         <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3">
+        <v>23330051920317</v>
+      </c>
+      <c r="B3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4">
+        <v>23330051920233</v>
+      </c>
+      <c r="B4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C4" t="s">
+        <v>25</v>
+      </c>
+      <c r="D4" t="s">
+        <v>28</v>
+      </c>
+      <c r="E4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G4">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Rivera Serra Alma Lilian - Estadisticos 20241.xlsx
+++ b/docentes/Rivera Serra Alma Lilian - Estadisticos 20241.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="32">
   <si>
     <t>Mat</t>
   </si>
@@ -79,6 +79,9 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>GAMBOA</t>
+  </si>
+  <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
@@ -88,6 +91,9 @@
     <t>GONZALEZ</t>
   </si>
   <si>
+    <t>APALE</t>
+  </si>
+  <si>
     <t>SARMIENTO</t>
   </si>
   <si>
@@ -95,6 +101,9 @@
   </si>
   <si>
     <t>TZITZIHUA</t>
+  </si>
+  <si>
+    <t>CRHIS AMINADAB</t>
   </si>
   <si>
     <t>EDUARDO</t>
@@ -812,7 +821,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -844,45 +853,45 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>23330051920236</v>
+        <v>22330051920239</v>
       </c>
       <c r="B2" t="s">
         <v>20</v>
       </c>
       <c r="C2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E2" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F2" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G2">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>23330051920317</v>
+        <v>23330051920236</v>
       </c>
       <c r="B3" t="s">
         <v>21</v>
       </c>
       <c r="C3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D3" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G3">
         <v>2</v>
@@ -890,24 +899,47 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>23330051920233</v>
+        <v>23330051920317</v>
       </c>
       <c r="B4" t="s">
         <v>22</v>
       </c>
       <c r="C4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D4" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5">
+        <v>23330051920233</v>
+      </c>
+      <c r="B5" t="s">
+        <v>23</v>
+      </c>
+      <c r="C5" t="s">
+        <v>27</v>
+      </c>
+      <c r="D5" t="s">
+        <v>31</v>
+      </c>
+      <c r="E5" t="s">
         <v>8</v>
       </c>
-      <c r="F4" t="s">
+      <c r="F5" t="s">
         <v>11</v>
       </c>
-      <c r="G4">
+      <c r="G5">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Rivera Serra Alma Lilian - Estadisticos 20241.xlsx
+++ b/docentes/Rivera Serra Alma Lilian - Estadisticos 20241.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="35">
   <si>
     <t>Mat</t>
   </si>
@@ -79,40 +79,49 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>LLANOS</t>
+  </si>
+  <si>
+    <t>ARELLANO</t>
+  </si>
+  <si>
+    <t>HUERTA</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
     <t>GAMBOA</t>
   </si>
   <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>ESTRADA</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
+    <t>SANTIAGO</t>
+  </si>
+  <si>
+    <t>FIERROS</t>
+  </si>
+  <si>
+    <t>VENTURA</t>
+  </si>
+  <si>
+    <t>FLORES</t>
   </si>
   <si>
     <t>APALE</t>
   </si>
   <si>
-    <t>SARMIENTO</t>
-  </si>
-  <si>
-    <t>SAN JUAN</t>
-  </si>
-  <si>
-    <t>TZITZIHUA</t>
+    <t>SERGIO</t>
+  </si>
+  <si>
+    <t>ALDO EMANUEL</t>
+  </si>
+  <si>
+    <t>NIDIA GABRIELA</t>
+  </si>
+  <si>
+    <t>AILYN</t>
   </si>
   <si>
     <t>CRHIS AMINADAB</t>
-  </si>
-  <si>
-    <t>EDUARDO</t>
-  </si>
-  <si>
-    <t>JOSE MARCOS</t>
-  </si>
-  <si>
-    <t>MIRIAM</t>
   </si>
 </sst>
 </file>
@@ -750,16 +759,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F2">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G2">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="H2">
-        <v>8.199999999999999</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -776,16 +785,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F3">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G3">
-        <v>89.47</v>
+        <v>94.73999999999999</v>
       </c>
       <c r="H3">
-        <v>7.5</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -802,16 +811,16 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F4">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="G4">
-        <v>92.86</v>
+        <v>78.56999999999999</v>
       </c>
       <c r="H4">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -821,7 +830,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -853,16 +862,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920239</v>
+        <v>21330051420317</v>
       </c>
       <c r="B2" t="s">
         <v>20</v>
       </c>
       <c r="C2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E2" t="s">
         <v>10</v>
@@ -871,76 +880,99 @@
         <v>13</v>
       </c>
       <c r="G2">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>23330051920236</v>
+        <v>22330051920231</v>
       </c>
       <c r="B3" t="s">
         <v>21</v>
       </c>
       <c r="C3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E3" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F3" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>23330051920317</v>
+        <v>22330051920369</v>
       </c>
       <c r="B4" t="s">
         <v>22</v>
       </c>
       <c r="C4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D4" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G4">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>23330051920233</v>
+        <v>22330051920366</v>
       </c>
       <c r="B5" t="s">
         <v>23</v>
       </c>
       <c r="C5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D5" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E5" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F5" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G5">
-        <v>1</v>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6">
+        <v>22330051920239</v>
+      </c>
+      <c r="B6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D6" t="s">
+        <v>34</v>
+      </c>
+      <c r="E6" t="s">
+        <v>10</v>
+      </c>
+      <c r="F6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G6">
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Rivera Serra Alma Lilian - Estadisticos 20241.xlsx
+++ b/docentes/Rivera Serra Alma Lilian - Estadisticos 20241.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="23">
   <si>
     <t>Mat</t>
   </si>
@@ -79,46 +79,10 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>LLANOS</t>
-  </si>
-  <si>
-    <t>ARELLANO</t>
-  </si>
-  <si>
-    <t>HUERTA</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
     <t>GAMBOA</t>
   </si>
   <si>
-    <t>SANTIAGO</t>
-  </si>
-  <si>
-    <t>FIERROS</t>
-  </si>
-  <si>
-    <t>VENTURA</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
     <t>APALE</t>
-  </si>
-  <si>
-    <t>SERGIO</t>
-  </si>
-  <si>
-    <t>ALDO EMANUEL</t>
-  </si>
-  <si>
-    <t>NIDIA GABRIELA</t>
-  </si>
-  <si>
-    <t>AILYN</t>
   </si>
   <si>
     <t>CRHIS AMINADAB</t>
@@ -830,7 +794,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -862,16 +826,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051420317</v>
+        <v>22330051920239</v>
       </c>
       <c r="B2" t="s">
         <v>20</v>
       </c>
       <c r="C2" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D2" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="E2" t="s">
         <v>10</v>
@@ -880,98 +844,6 @@
         <v>13</v>
       </c>
       <c r="G2">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3">
-        <v>22330051920231</v>
-      </c>
-      <c r="B3" t="s">
-        <v>21</v>
-      </c>
-      <c r="C3" t="s">
-        <v>26</v>
-      </c>
-      <c r="D3" t="s">
-        <v>31</v>
-      </c>
-      <c r="E3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
-        <v>22330051920369</v>
-      </c>
-      <c r="B4" t="s">
-        <v>22</v>
-      </c>
-      <c r="C4" t="s">
-        <v>27</v>
-      </c>
-      <c r="D4" t="s">
-        <v>32</v>
-      </c>
-      <c r="E4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F4" t="s">
-        <v>13</v>
-      </c>
-      <c r="G4">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>22330051920366</v>
-      </c>
-      <c r="B5" t="s">
-        <v>23</v>
-      </c>
-      <c r="C5" t="s">
-        <v>28</v>
-      </c>
-      <c r="D5" t="s">
-        <v>33</v>
-      </c>
-      <c r="E5" t="s">
-        <v>10</v>
-      </c>
-      <c r="F5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G5">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>22330051920239</v>
-      </c>
-      <c r="B6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C6" t="s">
-        <v>29</v>
-      </c>
-      <c r="D6" t="s">
-        <v>34</v>
-      </c>
-      <c r="E6" t="s">
-        <v>10</v>
-      </c>
-      <c r="F6" t="s">
-        <v>13</v>
-      </c>
-      <c r="G6">
         <v>2</v>
       </c>
     </row>
